--- a/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Dirty Chip - Sea Salted (2oz)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Dirty Chip - Salt &amp; Vinegar (2oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Dirty Chip - Mesquite Barbecue (2oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Dirty Chip - Cracked Pepper (2oz)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Tractor - Strawberry Dragon</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.19</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Tractor - Lemonade</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23.19</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Whipped Cream</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>52.32</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>52.32</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>52.32</v>
+      </c>
+      <c r="E8" t="n">
+        <v>52.32</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Half &amp; Half</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21.86</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Bread - GF</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.49</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Bagel - Plain GF</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>91.00</t>
-        </is>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="E11" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Cheddar - (Sliced)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>34.91</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>209.46</t>
-        </is>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="E12" t="n">
+        <v>209.46</v>
       </c>
     </row>
     <row r="13">
@@ -751,20 +685,14 @@
           <t>Sausage - Chicken Patty</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>50.68</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>101.36</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="E13" t="n">
+        <v>101.36</v>
       </c>
     </row>
     <row r="14">
@@ -778,20 +706,14 @@
           <t>Bleach</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>13.28</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>13.28</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13.28</v>
       </c>
     </row>
     <row r="15">
@@ -805,20 +727,14 @@
           <t>FRZ Fruit - Strawberry (Whole)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>87.48</t>
-        </is>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="E15" t="n">
+        <v>87.48</v>
       </c>
     </row>
     <row r="16">
@@ -832,20 +748,14 @@
           <t>FRZ Fruit - Pineapple (Chunk)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>50.79</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50.79</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50.79</v>
       </c>
     </row>
   </sheetData>
